--- a/InputData/Location/Location.xlsx
+++ b/InputData/Location/Location.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Personal\fusion-hcm-migration-mvp\InputData\Location\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01EED17E-A61B-40F4-B142-5BC2F72AFF82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{131CF681-D97B-4453-BE25-CF3491393434}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="77">
   <si>
     <t>SetCode</t>
   </si>
@@ -819,9 +819,7 @@
       <c r="W3" s="1"/>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A4" s="1"/>
       <c r="B4" s="1" t="s">
         <v>24</v>
       </c>
@@ -876,9 +874,7 @@
       <c r="W4" s="1"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A5" s="1"/>
       <c r="B5" s="1" t="s">
         <v>24</v>
       </c>
@@ -933,9 +929,7 @@
       <c r="W5" s="1"/>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A6" s="1"/>
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
@@ -990,9 +984,7 @@
       <c r="W6" s="1"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A7" s="1"/>
       <c r="B7" s="1" t="s">
         <v>24</v>
       </c>
@@ -1047,9 +1039,7 @@
       <c r="W7" s="1"/>
     </row>
     <row r="8" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A8" s="1"/>
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
@@ -1104,9 +1094,7 @@
       <c r="W8" s="1"/>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="A9" s="1"/>
       <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
